--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/140.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/140.xlsx
@@ -426,13 +426,13 @@
         <v>-12.83483788726785</v>
       </c>
       <c r="E2">
-        <v>-13.56948387121168</v>
+        <v>-11.9199011729116</v>
       </c>
       <c r="F2">
-        <v>-3.59552540194052</v>
+        <v>-3.335348651181423</v>
       </c>
       <c r="G2">
-        <v>-9.447165913173871</v>
+        <v>-9.713486059626081</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.66032045918257</v>
       </c>
       <c r="E3">
-        <v>-13.52638638408068</v>
+        <v>-11.78300540365973</v>
       </c>
       <c r="F3">
-        <v>-3.645850032962481</v>
+        <v>-3.069458681332379</v>
       </c>
       <c r="G3">
-        <v>-9.524447288242618</v>
+        <v>-9.933451947437415</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.61829677329303</v>
       </c>
       <c r="E4">
-        <v>-14.59753351195899</v>
+        <v>-12.52895828457323</v>
       </c>
       <c r="F4">
-        <v>-3.367188266758375</v>
+        <v>-2.451575818423679</v>
       </c>
       <c r="G4">
-        <v>-8.104325878806996</v>
+        <v>-8.822998967745221</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.69118140152787</v>
       </c>
       <c r="E5">
-        <v>-14.50766141680277</v>
+        <v>-14.5428657737384</v>
       </c>
       <c r="F5">
-        <v>-3.436826191419121</v>
+        <v>-2.970981471951481</v>
       </c>
       <c r="G5">
-        <v>-9.566011187488167</v>
+        <v>-8.688173690112862</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.81889422430377</v>
       </c>
       <c r="E6">
-        <v>-15.97636327781446</v>
+        <v>-14.49672515207424</v>
       </c>
       <c r="F6">
-        <v>-3.48279721487954</v>
+        <v>-3.07103842798303</v>
       </c>
       <c r="G6">
-        <v>-8.749448577499233</v>
+        <v>-7.996319330588273</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.93057144031035</v>
       </c>
       <c r="E7">
-        <v>-15.39981155257989</v>
+        <v>-14.89965065538072</v>
       </c>
       <c r="F7">
-        <v>-3.453645148241088</v>
+        <v>-3.130364843428349</v>
       </c>
       <c r="G7">
-        <v>-9.07105814500281</v>
+        <v>-6.887220364021641</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.96383350504467</v>
       </c>
       <c r="E8">
-        <v>-15.8472111991157</v>
+        <v>-16.51166966178717</v>
       </c>
       <c r="F8">
-        <v>-3.320324825014607</v>
+        <v>-3.52757649963859</v>
       </c>
       <c r="G8">
-        <v>-8.015507252533888</v>
+        <v>-8.114088677602307</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.85943921024575</v>
       </c>
       <c r="E9">
-        <v>-16.94932403225847</v>
+        <v>-17.37455227005272</v>
       </c>
       <c r="F9">
-        <v>-3.324477301924889</v>
+        <v>-3.292783387292157</v>
       </c>
       <c r="G9">
-        <v>-6.995415613336101</v>
+        <v>-7.412590698921821</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.58757839526107</v>
       </c>
       <c r="E10">
-        <v>-17.64937177215621</v>
+        <v>-17.99463168744902</v>
       </c>
       <c r="F10">
-        <v>-3.474213528817858</v>
+        <v>-2.619843780086162</v>
       </c>
       <c r="G10">
-        <v>-7.602486901599955</v>
+        <v>-6.808402895822672</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.13798129537427</v>
       </c>
       <c r="E11">
-        <v>-17.81995033107714</v>
+        <v>-18.88929965477441</v>
       </c>
       <c r="F11">
-        <v>-3.620541620580801</v>
+        <v>-2.937905773907528</v>
       </c>
       <c r="G11">
-        <v>-7.216109821166076</v>
+        <v>-7.091613445616243</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.54065026173811</v>
       </c>
       <c r="E12">
-        <v>-18.91693693164322</v>
+        <v>-19.94007317809222</v>
       </c>
       <c r="F12">
-        <v>-3.242808755277508</v>
+        <v>-2.168346644359445</v>
       </c>
       <c r="G12">
-        <v>-6.646980695327809</v>
+        <v>-6.095764931402538</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.84691729062042</v>
       </c>
       <c r="E13">
-        <v>-20.1384927952123</v>
+        <v>-19.7256952185691</v>
       </c>
       <c r="F13">
-        <v>-3.222397953439324</v>
+        <v>-2.662207913324167</v>
       </c>
       <c r="G13">
-        <v>-6.25338000452724</v>
+        <v>-6.525629338040284</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.13377363086483</v>
       </c>
       <c r="E14">
-        <v>-20.52255267580282</v>
+        <v>-20.12866147814165</v>
       </c>
       <c r="F14">
-        <v>-3.325585896065697</v>
+        <v>-2.304626913941883</v>
       </c>
       <c r="G14">
-        <v>-6.676841816092034</v>
+        <v>-6.038869895764623</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.479949639600564</v>
       </c>
       <c r="E15">
-        <v>-21.42870032473767</v>
+        <v>-20.2743968286565</v>
       </c>
       <c r="F15">
-        <v>-2.937248535952621</v>
+        <v>-2.316446903041765</v>
       </c>
       <c r="G15">
-        <v>-5.963045160733157</v>
+        <v>-6.613289273374646</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.952841273388019</v>
       </c>
       <c r="E16">
-        <v>-20.99505818223716</v>
+        <v>-20.79710046946586</v>
       </c>
       <c r="F16">
-        <v>-2.651457717570164</v>
+        <v>-2.310395562738871</v>
       </c>
       <c r="G16">
-        <v>-5.675199847184605</v>
+        <v>-5.843279554758943</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.597195272930616</v>
       </c>
       <c r="E17">
-        <v>-21.84997973319723</v>
+        <v>-22.57468048559273</v>
       </c>
       <c r="F17">
-        <v>-2.604203100465282</v>
+        <v>-1.895676037633447</v>
       </c>
       <c r="G17">
-        <v>-5.930826931544969</v>
+        <v>-3.996283161307537</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.425241608787472</v>
       </c>
       <c r="E18">
-        <v>-22.77377937381397</v>
+        <v>-24.60502180693174</v>
       </c>
       <c r="F18">
-        <v>-2.160607073550693</v>
+        <v>-1.101534624865913</v>
       </c>
       <c r="G18">
-        <v>-5.543138875077538</v>
+        <v>-4.342519877077753</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.428484818734853</v>
       </c>
       <c r="E19">
-        <v>-23.72945947144471</v>
+        <v>-24.04585036493861</v>
       </c>
       <c r="F19">
-        <v>-1.693013942752407</v>
+        <v>-1.054272089231454</v>
       </c>
       <c r="G19">
-        <v>-5.478099897413016</v>
+        <v>-3.269019206694903</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.571988996310891</v>
       </c>
       <c r="E20">
-        <v>-24.80136738295631</v>
+        <v>-25.77504816476754</v>
       </c>
       <c r="F20">
-        <v>-1.724202655198114</v>
+        <v>-0.5593703254802885</v>
       </c>
       <c r="G20">
-        <v>-4.906004522771562</v>
+        <v>-5.848404279253734</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.818475574842852</v>
       </c>
       <c r="E21">
-        <v>-25.36236832844854</v>
+        <v>-26.78806327180938</v>
       </c>
       <c r="F21">
-        <v>-1.914604490734779</v>
+        <v>-0.6119105610779499</v>
       </c>
       <c r="G21">
-        <v>-5.301379665981181</v>
+        <v>-6.125139401972492</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.118122956188383</v>
       </c>
       <c r="E22">
-        <v>-26.56352794508707</v>
+        <v>-27.72003227953596</v>
       </c>
       <c r="F22">
-        <v>-1.191215139739503</v>
+        <v>-0.75428097175821</v>
       </c>
       <c r="G22">
-        <v>-6.305809114232678</v>
+        <v>-4.368136878460634</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.430403443861284</v>
       </c>
       <c r="E23">
-        <v>-26.82713041707356</v>
+        <v>-26.92861804805946</v>
       </c>
       <c r="F23">
-        <v>-0.7904282674251576</v>
+        <v>-0.7026497833560108</v>
       </c>
       <c r="G23">
-        <v>-5.045600296526011</v>
+        <v>-5.314025949941197</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.711715795251166</v>
       </c>
       <c r="E24">
-        <v>-26.45368527955701</v>
+        <v>-28.78891969888445</v>
       </c>
       <c r="F24">
-        <v>-0.4437637529179975</v>
+        <v>-0.03581457060107703</v>
       </c>
       <c r="G24">
-        <v>-4.572169110591457</v>
+        <v>-4.787503545193351</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.934749429184119</v>
       </c>
       <c r="E25">
-        <v>-27.11062194690174</v>
+        <v>-27.53332329619971</v>
       </c>
       <c r="F25">
-        <v>-0.7335367998248263</v>
+        <v>-0.1265181594960405</v>
       </c>
       <c r="G25">
-        <v>-5.269982452086733</v>
+        <v>-5.21912254096691</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.07595650520857</v>
       </c>
       <c r="E26">
-        <v>-27.23588406642791</v>
+        <v>-28.60937476142833</v>
       </c>
       <c r="F26">
-        <v>-0.5134016775787431</v>
+        <v>-0.1771587398481323</v>
       </c>
       <c r="G26">
-        <v>-5.44628555478062</v>
+        <v>-4.741450546196549</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.1300338251569</v>
       </c>
       <c r="E27">
-        <v>-26.92357785648892</v>
+        <v>-26.70046899907902</v>
       </c>
       <c r="F27">
-        <v>-0.5531764516450048</v>
+        <v>0.2526891360145271</v>
       </c>
       <c r="G27">
-        <v>-5.579104641816181</v>
+        <v>-6.08281407725291</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.09349109628662</v>
       </c>
       <c r="E28">
-        <v>-27.80801600103099</v>
+        <v>-27.70269275256059</v>
       </c>
       <c r="F28">
-        <v>-0.2456080932193406</v>
+        <v>0.2210585696184127</v>
       </c>
       <c r="G28">
-        <v>-5.547131392997899</v>
+        <v>-5.508341730914259</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.977021671849311</v>
       </c>
       <c r="E29">
-        <v>-27.46644226358043</v>
+        <v>-28.80823364052716</v>
       </c>
       <c r="F29">
-        <v>-0.4445556058757172</v>
+        <v>0.3980274115803206</v>
       </c>
       <c r="G29">
-        <v>-5.322153339240108</v>
+        <v>-4.493229152207535</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.790364586155142</v>
       </c>
       <c r="E30">
-        <v>-27.10935397417959</v>
+        <v>-27.78568156722516</v>
       </c>
       <c r="F30">
-        <v>-0.5885018039418395</v>
+        <v>0.08413848284613759</v>
       </c>
       <c r="G30">
-        <v>-5.810475359010304</v>
+        <v>-4.626657379622321</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.551549286026388</v>
       </c>
       <c r="E31">
-        <v>-26.42899151079319</v>
+        <v>-29.37861305568928</v>
       </c>
       <c r="F31">
-        <v>-0.6142766177156165</v>
+        <v>-0.01689324417636424</v>
       </c>
       <c r="G31">
-        <v>-5.141894134626792</v>
+        <v>-6.142450244597341</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.275677849755633</v>
       </c>
       <c r="E32">
-        <v>-25.66377902992507</v>
+        <v>-28.22272006523142</v>
       </c>
       <c r="F32">
-        <v>-0.6380187449469269</v>
+        <v>-0.3330254923397672</v>
       </c>
       <c r="G32">
-        <v>-5.115254174672277</v>
+        <v>-5.153490975650858</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.981098146815281</v>
       </c>
       <c r="E33">
-        <v>-25.84330132501114</v>
+        <v>-27.86530572570203</v>
       </c>
       <c r="F33">
-        <v>-0.5547878724139644</v>
+        <v>-0.4073020916268351</v>
       </c>
       <c r="G33">
-        <v>-5.571093121611145</v>
+        <v>-5.616361521315138</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.68381625968285</v>
       </c>
       <c r="E34">
-        <v>-26.18220326279718</v>
+        <v>-27.96327473238397</v>
       </c>
       <c r="F34">
-        <v>-0.7141086875071729</v>
+        <v>-0.04423117568867998</v>
       </c>
       <c r="G34">
-        <v>-4.692451161669796</v>
+        <v>-4.587099670973569</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.400421201493577</v>
       </c>
       <c r="E35">
-        <v>-25.10182257641722</v>
+        <v>-26.62300492270381</v>
       </c>
       <c r="F35">
-        <v>-1.038032768774538</v>
+        <v>-0.3490019176147204</v>
       </c>
       <c r="G35">
-        <v>-4.857581173168643</v>
+        <v>-3.9965413838596</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.147287737101017</v>
       </c>
       <c r="E36">
-        <v>-24.41190503287464</v>
+        <v>-26.42370678162624</v>
       </c>
       <c r="F36">
-        <v>-0.8139336306221099</v>
+        <v>0.05402985783476054</v>
       </c>
       <c r="G36">
-        <v>-4.709063479185859</v>
+        <v>-4.918832886736238</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.93712624548611</v>
       </c>
       <c r="E37">
-        <v>-23.61036513351698</v>
+        <v>-25.88416174598235</v>
       </c>
       <c r="F37">
-        <v>-1.201696897340839</v>
+        <v>0.09581593841363036</v>
       </c>
       <c r="G37">
-        <v>-5.070071849152304</v>
+        <v>-5.026816261136186</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.780207769353876</v>
       </c>
       <c r="E38">
-        <v>-24.29523795701502</v>
+        <v>-24.88653892209257</v>
       </c>
       <c r="F38">
-        <v>-0.9983221347978516</v>
+        <v>-0.8333561999690593</v>
       </c>
       <c r="G38">
-        <v>-5.01117062291759</v>
+        <v>-6.02680295727398</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.678367576374798</v>
       </c>
       <c r="E39">
-        <v>-23.12137145322072</v>
+        <v>-24.3236813022572</v>
       </c>
       <c r="F39">
-        <v>-1.004279244598777</v>
+        <v>-0.05099201624169098</v>
       </c>
       <c r="G39">
-        <v>-5.336693255248587</v>
+        <v>-4.266956675143889</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.632851431006124</v>
       </c>
       <c r="E40">
-        <v>-23.17199073567846</v>
+        <v>-25.60115476287299</v>
       </c>
       <c r="F40">
-        <v>-0.8628392611438377</v>
+        <v>-0.2653901638090947</v>
       </c>
       <c r="G40">
-        <v>-5.090895180594319</v>
+        <v>-3.835599212467931</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.633818430530864</v>
       </c>
       <c r="E41">
-        <v>-22.80122192630045</v>
+        <v>-23.75495025163388</v>
       </c>
       <c r="F41">
-        <v>-0.8794927206976412</v>
+        <v>-1.238090459277638</v>
       </c>
       <c r="G41">
-        <v>-4.717379569580508</v>
+        <v>-4.719852547098344</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.675415067819877</v>
       </c>
       <c r="E42">
-        <v>-22.72062414591193</v>
+        <v>-24.19945620327879</v>
       </c>
       <c r="F42">
-        <v>-0.7647072996525055</v>
+        <v>-0.4608337271275615</v>
       </c>
       <c r="G42">
-        <v>-5.024204240705701</v>
+        <v>-3.784143403151039</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.743100823899325</v>
       </c>
       <c r="E43">
-        <v>-21.8837304499764</v>
+        <v>-22.47555218956483</v>
       </c>
       <c r="F43">
-        <v>-0.7213478072466466</v>
+        <v>-0.6864951911655707</v>
       </c>
       <c r="G43">
-        <v>-4.659246389910906</v>
+        <v>-4.631987357940547</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.831282888189587</v>
       </c>
       <c r="E44">
-        <v>-20.89486116634344</v>
+        <v>-23.76703222028635</v>
       </c>
       <c r="F44">
-        <v>-0.7126009994756746</v>
+        <v>-0.3618441888830189</v>
       </c>
       <c r="G44">
-        <v>-5.536160245080755</v>
+        <v>-5.324765359670593</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.929387054398332</v>
       </c>
       <c r="E45">
-        <v>-21.46289936044359</v>
+        <v>-21.22530391468315</v>
       </c>
       <c r="F45">
-        <v>-0.5200191927464068</v>
+        <v>0.03911134811132094</v>
       </c>
       <c r="G45">
-        <v>-4.635572678759578</v>
+        <v>-4.712506446546701</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.038310333805537</v>
       </c>
       <c r="E46">
-        <v>-22.04839482184331</v>
+        <v>-21.29479787680486</v>
       </c>
       <c r="F46">
-        <v>-0.6887472209773255</v>
+        <v>-0.697727625370825</v>
       </c>
       <c r="G46">
-        <v>-4.226266759920706</v>
+        <v>-4.309454148231513</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.156207244004385</v>
       </c>
       <c r="E47">
-        <v>-20.48829929840881</v>
+        <v>-20.55495390732771</v>
       </c>
       <c r="F47">
-        <v>-0.7575180666493682</v>
+        <v>-0.7860833702461495</v>
       </c>
       <c r="G47">
-        <v>-4.789158817962986</v>
+        <v>-4.168597056626602</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.290613792744445</v>
       </c>
       <c r="E48">
-        <v>-20.07422469209545</v>
+        <v>-22.18493737012258</v>
       </c>
       <c r="F48">
-        <v>-0.5857002281774271</v>
+        <v>-0.06737862134874294</v>
       </c>
       <c r="G48">
-        <v>-4.193518843446236</v>
+        <v>-4.677792066021904</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.44766369861769</v>
       </c>
       <c r="E49">
-        <v>-18.94535763451536</v>
+        <v>-20.09553569077554</v>
       </c>
       <c r="F49">
-        <v>-0.6681542929588664</v>
+        <v>-0.4777920500700871</v>
       </c>
       <c r="G49">
-        <v>-5.060835427097737</v>
+        <v>-3.833318246591373</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.637273287340829</v>
       </c>
       <c r="E50">
-        <v>-19.87083733898895</v>
+        <v>-20.92515212898075</v>
       </c>
       <c r="F50">
-        <v>-0.6961122453370767</v>
+        <v>-0.8844964395374721</v>
       </c>
       <c r="G50">
-        <v>-4.302439102233797</v>
+        <v>-4.031192864019151</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.868771184971202</v>
       </c>
       <c r="E51">
-        <v>-18.33065351576617</v>
+        <v>-20.8044501827803</v>
       </c>
       <c r="F51">
-        <v>-0.5089736358391744</v>
+        <v>-0.2584329437225693</v>
       </c>
       <c r="G51">
-        <v>-4.667976298497964</v>
+        <v>-3.848017068785738</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.145948057377296</v>
       </c>
       <c r="E52">
-        <v>-18.57365143101777</v>
+        <v>-20.21208049783695</v>
       </c>
       <c r="F52">
-        <v>-0.859038366946783</v>
+        <v>-0.2692615329193865</v>
       </c>
       <c r="G52">
-        <v>-4.535332670375985</v>
+        <v>-4.51160267995049</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.476169149973831</v>
       </c>
       <c r="E53">
-        <v>-18.06229161759762</v>
+        <v>-19.71758925009537</v>
       </c>
       <c r="F53">
-        <v>-0.8797342358497457</v>
+        <v>-0.4757023501146648</v>
       </c>
       <c r="G53">
-        <v>-4.41939074449963</v>
+        <v>-3.0866114580266</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.854203724045258</v>
       </c>
       <c r="E54">
-        <v>-18.31379400703562</v>
+        <v>-17.80227569702521</v>
       </c>
       <c r="F54">
-        <v>-0.8739125329045904</v>
+        <v>0.1488590006394438</v>
       </c>
       <c r="G54">
-        <v>-3.876040836775668</v>
+        <v>-3.928622231575913</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.2827911390882</v>
       </c>
       <c r="E55">
-        <v>-17.80293232575632</v>
+        <v>-17.36094873413368</v>
       </c>
       <c r="F55">
-        <v>-0.4734724921857261</v>
+        <v>-0.1068683283502256</v>
       </c>
       <c r="G55">
-        <v>-4.468525861393493</v>
+        <v>-3.832993813128525</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.7487122989703</v>
       </c>
       <c r="E56">
-        <v>-16.79607141489089</v>
+        <v>-19.5252015603535</v>
       </c>
       <c r="F56">
-        <v>-0.5218943005502872</v>
+        <v>-0.1671140850794576</v>
       </c>
       <c r="G56">
-        <v>-4.49398064604495</v>
+        <v>-3.511549772901911</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.24944721253543</v>
       </c>
       <c r="E57">
-        <v>-17.26282575933548</v>
+        <v>-17.02885309278118</v>
       </c>
       <c r="F57">
-        <v>-0.664183150375902</v>
+        <v>-0.2140448343246324</v>
       </c>
       <c r="G57">
-        <v>-4.311496754829243</v>
+        <v>-4.69116335945502</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.7659963825772</v>
       </c>
       <c r="E58">
-        <v>-16.81221542472823</v>
+        <v>-17.07086827462434</v>
       </c>
       <c r="F58">
-        <v>-0.5692645281869965</v>
+        <v>-0.4110855650588199</v>
       </c>
       <c r="G58">
-        <v>-4.780352766828525</v>
+        <v>-5.727162169969006</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.29228920884649</v>
       </c>
       <c r="E59">
-        <v>-17.95047906587423</v>
+        <v>-16.8454951802106</v>
       </c>
       <c r="F59">
-        <v>-0.3117151455416141</v>
+        <v>-0.3228145484499714</v>
       </c>
       <c r="G59">
-        <v>-4.753014281765223</v>
+        <v>-4.521795849665906</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.80819359426574</v>
       </c>
       <c r="E60">
-        <v>-17.45655840585762</v>
+        <v>-16.99967613474976</v>
       </c>
       <c r="F60">
-        <v>-0.5269795802447632</v>
+        <v>-0.1932151422718151</v>
       </c>
       <c r="G60">
-        <v>-5.351309313804469</v>
+        <v>-4.713168555654556</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.30937159720252</v>
       </c>
       <c r="E61">
-        <v>-16.5282212342852</v>
+        <v>-15.26485849867731</v>
       </c>
       <c r="F61">
-        <v>-0.311768991542739</v>
+        <v>-0.04247880509324623</v>
       </c>
       <c r="G61">
-        <v>-5.7774294934373</v>
+        <v>-6.300608247190482</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.77971134891456</v>
       </c>
       <c r="E62">
-        <v>-15.69905311500675</v>
+        <v>-16.54118172689515</v>
       </c>
       <c r="F62">
-        <v>-0.220131808010624</v>
+        <v>0.4680066248658435</v>
       </c>
       <c r="G62">
-        <v>-4.79313809370119</v>
+        <v>-3.511033327797784</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.21731230391087</v>
       </c>
       <c r="E63">
-        <v>-16.03196388168064</v>
+        <v>-17.0498289843847</v>
       </c>
       <c r="F63">
-        <v>-0.3834831546586258</v>
+        <v>-0.2594853163033788</v>
       </c>
       <c r="G63">
-        <v>-5.441236972833232</v>
+        <v>-4.720206775471046</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.60980808889098</v>
       </c>
       <c r="E64">
-        <v>-15.28890922413205</v>
+        <v>-15.96520964633357</v>
       </c>
       <c r="F64">
-        <v>-0.894339963654886</v>
+        <v>-0.3690516345041838</v>
       </c>
       <c r="G64">
-        <v>-6.378396135726737</v>
+        <v>-5.729770879853952</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.95736874127106</v>
       </c>
       <c r="E65">
-        <v>-15.93615948557436</v>
+        <v>-15.9461583561833</v>
       </c>
       <c r="F65">
-        <v>-0.3261197426954935</v>
+        <v>-0.4527243609875539</v>
       </c>
       <c r="G65">
-        <v>-6.339215829269463</v>
+        <v>-7.263427448558879</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.25112395728626</v>
       </c>
       <c r="E66">
-        <v>-14.70530666486754</v>
+        <v>-14.37049846758444</v>
       </c>
       <c r="F66">
-        <v>-0.4441786838678426</v>
+        <v>-0.881454140473913</v>
       </c>
       <c r="G66">
-        <v>-6.270187644230119</v>
+        <v>-6.027147254010064</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.49227546539237</v>
       </c>
       <c r="E67">
-        <v>-16.30177036305764</v>
+        <v>-15.72233852835419</v>
       </c>
       <c r="F67">
-        <v>-0.5593584476859227</v>
+        <v>-0.750014468022016</v>
       </c>
       <c r="G67">
-        <v>-6.7554904464685</v>
+        <v>-7.203973361219107</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.67547698964244</v>
       </c>
       <c r="E68">
-        <v>-15.88114758332918</v>
+        <v>-15.25913450753162</v>
       </c>
       <c r="F68">
-        <v>-0.603239771190919</v>
+        <v>-0.08640922348162106</v>
       </c>
       <c r="G68">
-        <v>-6.898410007944377</v>
+        <v>-5.897079230317638</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.80424850159789</v>
       </c>
       <c r="E69">
-        <v>-14.99916840017328</v>
+        <v>-14.02033874341534</v>
       </c>
       <c r="F69">
-        <v>-0.8588206073834102</v>
+        <v>-0.6867169099937322</v>
       </c>
       <c r="G69">
-        <v>-7.528158533152238</v>
+        <v>-6.230871605405735</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.87817522701402</v>
       </c>
       <c r="E70">
-        <v>-14.40092981291598</v>
+        <v>-14.12433967747549</v>
       </c>
       <c r="F70">
-        <v>-0.6583044340177908</v>
+        <v>0.2168562059717942</v>
       </c>
       <c r="G70">
-        <v>-7.978021945392721</v>
+        <v>-6.113277717305283</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.90290087702666</v>
       </c>
       <c r="E71">
-        <v>-14.18577295586355</v>
+        <v>-16.41931143440073</v>
       </c>
       <c r="F71">
-        <v>-1.198370323065459</v>
+        <v>0.01193970572012634</v>
       </c>
       <c r="G71">
-        <v>-6.644524270537669</v>
+        <v>-7.785603107013662</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.88096936248012</v>
       </c>
       <c r="E72">
-        <v>-15.6475417231695</v>
+        <v>-15.72278231880695</v>
       </c>
       <c r="F72">
-        <v>-0.8638282854880297</v>
+        <v>-0.7843175381504345</v>
       </c>
       <c r="G72">
-        <v>-7.927824143380753</v>
+        <v>-7.402864316127442</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.81765901845416</v>
       </c>
       <c r="E73">
-        <v>-15.1267038136513</v>
+        <v>-15.49287622191153</v>
       </c>
       <c r="F73">
-        <v>-0.9708385023413154</v>
+        <v>-0.6209265988545467</v>
       </c>
       <c r="G73">
-        <v>-7.260931297222268</v>
+        <v>-7.538590062146482</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.71707097655347</v>
       </c>
       <c r="E74">
-        <v>-14.93430253848741</v>
+        <v>-15.42545177241132</v>
       </c>
       <c r="F74">
-        <v>-1.313899294037893</v>
+        <v>-0.6125218715613095</v>
       </c>
       <c r="G74">
-        <v>-7.084489151615732</v>
+        <v>-7.774324078361365</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.58331320095605</v>
       </c>
       <c r="E75">
-        <v>-15.47672768360018</v>
+        <v>-15.87422354657146</v>
       </c>
       <c r="F75">
-        <v>-1.241179477665702</v>
+        <v>-0.8663036178338616</v>
       </c>
       <c r="G75">
-        <v>-6.79405830200101</v>
+        <v>-6.511890574052309</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.42173099546559</v>
       </c>
       <c r="E76">
-        <v>-15.71879726168019</v>
+        <v>-17.24761914361772</v>
       </c>
       <c r="F76">
-        <v>-1.146035177383847</v>
+        <v>-1.31569917581079</v>
       </c>
       <c r="G76">
-        <v>-7.408525348999595</v>
+        <v>-5.116604877252299</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.23386310219134</v>
       </c>
       <c r="E77">
-        <v>-15.38447813958992</v>
+        <v>-16.93172185379066</v>
       </c>
       <c r="F77">
-        <v>-1.691421526454433</v>
+        <v>-0.9126531470080701</v>
       </c>
       <c r="G77">
-        <v>-6.681152146384166</v>
+        <v>-7.549011659504107</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.02630341841179</v>
       </c>
       <c r="E78">
-        <v>-16.72831638678813</v>
+        <v>-18.44578091046318</v>
       </c>
       <c r="F78">
-        <v>-1.291152525974436</v>
+        <v>-1.440884001749659</v>
       </c>
       <c r="G78">
-        <v>-6.911460178460183</v>
+        <v>-7.640544933119417</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.79945982754689</v>
       </c>
       <c r="E79">
-        <v>-17.20755573407186</v>
+        <v>-15.89252311003645</v>
       </c>
       <c r="F79">
-        <v>-1.961486145096576</v>
+        <v>-1.373737246493899</v>
       </c>
       <c r="G79">
-        <v>-7.165888845335331</v>
+        <v>-6.374847230908639</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.56287861308087</v>
       </c>
       <c r="E80">
-        <v>-17.05011427824719</v>
+        <v>-17.32017435416862</v>
       </c>
       <c r="F80">
-        <v>-1.492337815089329</v>
+        <v>-0.8967820381764937</v>
       </c>
       <c r="G80">
-        <v>-6.524536858012325</v>
+        <v>-6.14990228260624</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.31815139875181</v>
       </c>
       <c r="E81">
-        <v>-18.31712243543125</v>
+        <v>-19.51960889495403</v>
       </c>
       <c r="F81">
-        <v>-0.8710887852573618</v>
+        <v>-2.047505923746627</v>
       </c>
       <c r="G81">
-        <v>-6.567140268557205</v>
+        <v>-7.472216934629634</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.07905202026126</v>
       </c>
       <c r="E82">
-        <v>-19.62025422977451</v>
+        <v>-19.02134542836407</v>
       </c>
       <c r="F82">
-        <v>-1.16425492208802</v>
+        <v>-1.439726312725473</v>
       </c>
       <c r="G82">
-        <v>-7.008528684217154</v>
+        <v>-7.352285801378456</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.84818176694633</v>
       </c>
       <c r="E83">
-        <v>-19.462319170283</v>
+        <v>-18.66364126649819</v>
       </c>
       <c r="F83">
-        <v>-1.411544265960228</v>
+        <v>-1.676265460843678</v>
       </c>
       <c r="G83">
-        <v>-6.902498531685377</v>
+        <v>-5.14021899858392</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.64128702873564</v>
       </c>
       <c r="E84">
-        <v>-19.35154816758137</v>
+        <v>-18.56605265163289</v>
       </c>
       <c r="F84">
-        <v>-2.008794608202583</v>
+        <v>-2.202341683687311</v>
       </c>
       <c r="G84">
-        <v>-6.439578327838008</v>
+        <v>-6.635628834673648</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.46091799113591</v>
       </c>
       <c r="E85">
-        <v>-20.80877940393164</v>
+        <v>-19.0518854570718</v>
       </c>
       <c r="F85">
-        <v>-1.849872887000065</v>
+        <v>-2.130553086393399</v>
       </c>
       <c r="G85">
-        <v>-6.295490143786769</v>
+        <v>-5.478738832702096</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.32324750259914</v>
       </c>
       <c r="E86">
-        <v>-21.34461561936324</v>
+        <v>-20.89781373139645</v>
       </c>
       <c r="F86">
-        <v>-1.746066507213714</v>
+        <v>-2.746073851929221</v>
       </c>
       <c r="G86">
-        <v>-5.925364531405171</v>
+        <v>-6.107735864072543</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.23175541367279</v>
       </c>
       <c r="E87">
-        <v>-22.86707499531999</v>
+        <v>-24.27879053941917</v>
       </c>
       <c r="F87">
-        <v>-2.337325689977961</v>
+        <v>-1.839103686775077</v>
       </c>
       <c r="G87">
-        <v>-5.889590776307807</v>
+        <v>-5.60877044039359</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.20194111727953</v>
       </c>
       <c r="E88">
-        <v>-23.62995531207416</v>
+        <v>-24.40807394386415</v>
       </c>
       <c r="F88">
-        <v>-2.660175226781701</v>
+        <v>-2.428162310169822</v>
       </c>
       <c r="G88">
-        <v>-5.224243954916163</v>
+        <v>-7.100012299649374</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.2377976903675</v>
       </c>
       <c r="E89">
-        <v>-25.38239324051045</v>
+        <v>-25.09433700888254</v>
       </c>
       <c r="F89">
-        <v>-2.300603509063709</v>
+        <v>-1.989486857534503</v>
       </c>
       <c r="G89">
-        <v>-5.510083077867916</v>
+        <v>-4.732366409236789</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.3508867394004</v>
       </c>
       <c r="E90">
-        <v>-27.01668328208662</v>
+        <v>-25.24302492445039</v>
       </c>
       <c r="F90">
-        <v>-2.677725855736601</v>
+        <v>-2.482360685860948</v>
       </c>
       <c r="G90">
-        <v>-5.783898299421035</v>
+        <v>-4.447252295758137</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.54407717414888</v>
       </c>
       <c r="E91">
-        <v>-27.95431288232279</v>
+        <v>-29.56183511403962</v>
       </c>
       <c r="F91">
-        <v>-2.428904276391205</v>
+        <v>-2.847526052872272</v>
       </c>
       <c r="G91">
-        <v>-5.025038498181598</v>
+        <v>-5.63025588094346</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.82035754980284</v>
       </c>
       <c r="E92">
-        <v>-29.8458587395637</v>
+        <v>-29.42166072960619</v>
       </c>
       <c r="F92">
-        <v>-2.678679246697695</v>
+        <v>-3.568963486326769</v>
       </c>
       <c r="G92">
-        <v>-5.77556234575315</v>
+        <v>-3.847285438221558</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-14.17726975066386</v>
       </c>
       <c r="E93">
-        <v>-32.08346152352276</v>
+        <v>-31.55176659757118</v>
       </c>
       <c r="F93">
-        <v>-2.72661723290509</v>
+        <v>-3.491407032088826</v>
       </c>
       <c r="G93">
-        <v>-5.84016102086095</v>
+        <v>-4.81748715614253</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.60234485463543</v>
       </c>
       <c r="E94">
-        <v>-34.13971024465965</v>
+        <v>-34.33356515998</v>
       </c>
       <c r="F94">
-        <v>-3.451913365822555</v>
+        <v>-3.483980243198373</v>
       </c>
       <c r="G94">
-        <v>-5.987493539540674</v>
+        <v>-5.590482986834655</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-15.08423753430958</v>
       </c>
       <c r="E95">
-        <v>-35.44493872246846</v>
+        <v>-35.09705908496222</v>
       </c>
       <c r="F95">
-        <v>-3.497453621273974</v>
+        <v>-4.172961999474812</v>
       </c>
       <c r="G95">
-        <v>-5.872140890770309</v>
+        <v>-5.004592568931058</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-15.59534005328195</v>
       </c>
       <c r="E96">
-        <v>-37.97071547837963</v>
+        <v>-36.12134782804616</v>
       </c>
       <c r="F96">
-        <v>-3.514307419626081</v>
+        <v>-4.035022797945952</v>
       </c>
       <c r="G96">
-        <v>-5.844630257338966</v>
+        <v>-5.541192274300447</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-16.1151770094164</v>
       </c>
       <c r="E97">
-        <v>-39.38442581527919</v>
+        <v>-38.43213528044319</v>
       </c>
       <c r="F97">
-        <v>-3.628086395561955</v>
+        <v>-4.112706740510087</v>
       </c>
       <c r="G97">
-        <v>-6.450483264844367</v>
+        <v>-6.493692505222935</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-16.60814311300292</v>
       </c>
       <c r="E98">
-        <v>-42.26863808160848</v>
+        <v>-40.68753270301539</v>
       </c>
       <c r="F98">
-        <v>-3.932530894069415</v>
+        <v>-4.28735070218813</v>
       </c>
       <c r="G98">
-        <v>-5.967573987030879</v>
+        <v>-5.836118844757499</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.05335319635928</v>
       </c>
       <c r="E99">
-        <v>-43.3912082960809</v>
+        <v>-44.15378746931356</v>
       </c>
       <c r="F99">
-        <v>-4.656721600257903</v>
+        <v>-3.793877441172691</v>
       </c>
       <c r="G99">
-        <v>-6.470101557710088</v>
+        <v>-7.579548131558345</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-17.41678781943963</v>
       </c>
       <c r="E100">
-        <v>-46.84070770855068</v>
+        <v>-45.88285394339626</v>
       </c>
       <c r="F100">
-        <v>-4.324974803621225</v>
+        <v>-4.542141269128817</v>
       </c>
       <c r="G100">
-        <v>-6.618480208780223</v>
+        <v>-6.980415531497663</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.68699241469814</v>
       </c>
       <c r="E101">
-        <v>-48.4394854569587</v>
+        <v>-46.35019925369885</v>
       </c>
       <c r="F101">
-        <v>-4.797427536021036</v>
+        <v>-4.718526515460885</v>
       </c>
       <c r="G101">
-        <v>-7.378300068226049</v>
+        <v>-7.586685667741014</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.84223235888091</v>
       </c>
       <c r="E102">
-        <v>-51.11314292794586</v>
+        <v>-50.82611352779919</v>
       </c>
       <c r="F102">
-        <v>-4.560996079905081</v>
+        <v>-5.075334666356436</v>
       </c>
       <c r="G102">
-        <v>-8.170136213582168</v>
+        <v>-8.070488792850105</v>
       </c>
     </row>
   </sheetData>
